--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,50 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130757655</v>
+        <v>130758082</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490214</v>
+        <v>490186</v>
       </c>
       <c r="R6" t="n">
-        <v>6763590</v>
+        <v>6763602</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,45 +1220,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130758082</v>
+        <v>130757655</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490186</v>
+        <v>490214</v>
       </c>
       <c r="R7" t="n">
-        <v>6763602</v>
+        <v>6763590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130754307</v>
+        <v>130757425</v>
       </c>
       <c r="B11" t="n">
         <v>79211</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490501</v>
+        <v>490361</v>
       </c>
       <c r="R11" t="n">
-        <v>6763773</v>
+        <v>6763574</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130757425</v>
+        <v>130754307</v>
       </c>
       <c r="B12" t="n">
         <v>79211</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490361</v>
+        <v>490501</v>
       </c>
       <c r="R12" t="n">
-        <v>6763574</v>
+        <v>6763773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1887,40 +1887,35 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130757194</v>
+        <v>130757199</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
@@ -1999,35 +1994,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130757199</v>
+        <v>130757194</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130756109</v>
+        <v>130755955</v>
       </c>
       <c r="B15" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130755955</v>
+        <v>130756109</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,21 +2224,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130755667</v>
+        <v>130757159</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,39 +2545,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490444</v>
+        <v>490482</v>
       </c>
       <c r="R19" t="n">
-        <v>6763770</v>
+        <v>6763574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,12 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2758,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130757159</v>
+        <v>130755667</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,34 +2759,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490482</v>
+        <v>490444</v>
       </c>
       <c r="R21" t="n">
-        <v>6763574</v>
+        <v>6763770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2833,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130757715</v>
+        <v>130757236</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490186</v>
+        <v>490467</v>
       </c>
       <c r="R22" t="n">
-        <v>6763602</v>
+        <v>6763573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130757236</v>
+        <v>130757715</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,21 +2988,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3013,14 +3013,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490467</v>
+        <v>490186</v>
       </c>
       <c r="R23" t="n">
-        <v>6763573</v>
+        <v>6763602</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,45 +3089,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130754851</v>
+        <v>130757247</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490449</v>
+        <v>490467</v>
       </c>
       <c r="R24" t="n">
-        <v>6763949</v>
+        <v>6763573</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3159,7 +3164,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3169,12 +3174,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3201,7 +3201,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130757412</v>
+        <v>130754851</v>
       </c>
       <c r="B25" t="n">
         <v>79211</v>
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490381</v>
+        <v>490449</v>
       </c>
       <c r="R25" t="n">
-        <v>6763583</v>
+        <v>6763949</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3281,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,50 +3313,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130757247</v>
+        <v>130757412</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490467</v>
+        <v>490381</v>
       </c>
       <c r="R26" t="n">
-        <v>6763573</v>
+        <v>6763583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130754953</v>
+        <v>130754014</v>
       </c>
       <c r="B30" t="n">
         <v>79211</v>
@@ -3782,14 +3782,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490440</v>
+        <v>490548</v>
       </c>
       <c r="R30" t="n">
-        <v>6764028</v>
+        <v>6763654</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3832,11 +3832,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3863,50 +3858,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130758028</v>
+        <v>130754953</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490175</v>
+        <v>490440</v>
       </c>
       <c r="R31" t="n">
-        <v>6763613</v>
+        <v>6764028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,7 +3928,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3948,7 +3938,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,45 +3970,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130754014</v>
+        <v>130758028</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490548</v>
+        <v>490175</v>
       </c>
       <c r="R32" t="n">
-        <v>6763654</v>
+        <v>6763613</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,10 +4082,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130758572</v>
+        <v>130758032</v>
       </c>
       <c r="B33" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4093,39 +4093,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490494</v>
+        <v>490175</v>
       </c>
       <c r="R33" t="n">
-        <v>6763540</v>
+        <v>6763613</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4194,10 +4189,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130758032</v>
+        <v>130758572</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4205,34 +4200,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490175</v>
+        <v>490494</v>
       </c>
       <c r="R34" t="n">
-        <v>6763613</v>
+        <v>6763540</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4411,6 +4411,2495 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130789469</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>490373</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6763590</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130789471</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>490498</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6763669</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130789490</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>490470</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6763909</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130789477</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490435</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6764047</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130789496</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>490526</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6763737</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130789482</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>490451</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6764011</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130789470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>490376</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6763596</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130789473</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>490444</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6763969</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130789474</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>490445</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6763972</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130789495</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>490496</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6763849</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130789472</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>490450</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6763926</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130789476</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>490438</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6764018</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130789475</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>490441</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6763984</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130789468</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>490321</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6763593</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130789489</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>490467</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6763913</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130789487</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>490472</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6763924</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130789497</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>490525</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6763706</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130789459</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>490499</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6763662</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130789491</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>490481</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6763891</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130789493</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>490482</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6763883</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130789498</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>490523</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6763700</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130789492</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>490481</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6763889</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130789494</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>490480</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6763872</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130754287</v>
+        <v>130789469</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490501</v>
+        <v>490373</v>
       </c>
       <c r="R3" t="n">
-        <v>6763773</v>
+        <v>6763590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,28 +876,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130758328</v>
+        <v>130754287</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +906,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490200</v>
+        <v>490501</v>
       </c>
       <c r="R4" t="n">
-        <v>6763553</v>
+        <v>6763773</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +980,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,17 +1000,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130755448</v>
+        <v>130789471</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,14 +1038,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490441</v>
+        <v>490498</v>
       </c>
       <c r="R5" t="n">
-        <v>6763800</v>
+        <v>6763669</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,28 +1096,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130758082</v>
+        <v>130758328</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490186</v>
+        <v>490200</v>
       </c>
       <c r="R6" t="n">
-        <v>6763602</v>
+        <v>6763553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,57 +1215,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130757655</v>
+        <v>130789490</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490214</v>
+        <v>490470</v>
       </c>
       <c r="R7" t="n">
-        <v>6763590</v>
+        <v>6763909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,28 +1311,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130754257</v>
+        <v>130755448</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,14 +1361,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490525</v>
+        <v>490441</v>
       </c>
       <c r="R8" t="n">
-        <v>6763729</v>
+        <v>6763800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,11 +1413,6 @@
           <t>11:43</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på tallstam</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1437,17 +1430,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130754083</v>
+        <v>130789477</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490529</v>
+        <v>490435</v>
       </c>
       <c r="R9" t="n">
-        <v>6763665</v>
+        <v>6764047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 bild, tall med gran till höger</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,28 +1526,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130757152</v>
+        <v>130789496</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,39 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490482</v>
+        <v>490526</v>
       </c>
       <c r="R10" t="n">
-        <v>6763574</v>
+        <v>6763737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,12 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,28 +1634,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130757425</v>
+        <v>130789482</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490361</v>
+        <v>490451</v>
       </c>
       <c r="R11" t="n">
-        <v>6763574</v>
+        <v>6764011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,63 +1742,69 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130754307</v>
+        <v>130757655</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490501</v>
+        <v>490214</v>
       </c>
       <c r="R12" t="n">
-        <v>6763773</v>
+        <v>6763590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,7 +1836,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1860,7 +1846,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,17 +1866,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130757199</v>
+        <v>130758082</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,14 +1904,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490467</v>
+        <v>490186</v>
       </c>
       <c r="R13" t="n">
-        <v>6763573</v>
+        <v>6763602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,57 +1973,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130757194</v>
+        <v>130754257</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490467</v>
+        <v>490525</v>
       </c>
       <c r="R14" t="n">
-        <v>6763573</v>
+        <v>6763729</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2050,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2079,7 +2060,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,17 +2085,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130755955</v>
+        <v>130757152</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,34 +2103,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490486</v>
+        <v>490482</v>
       </c>
       <c r="R15" t="n">
-        <v>6763627</v>
+        <v>6763574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2167,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2186,7 +2177,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,17 +2202,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130756109</v>
+        <v>130754083</v>
       </c>
       <c r="B16" t="n">
-        <v>91761</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,34 +2220,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490486</v>
+        <v>490529</v>
       </c>
       <c r="R16" t="n">
-        <v>6763627</v>
+        <v>6763665</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,12 +2295,18 @@
           <t>11:43</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bild, tall med gran till vänster</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,17 +2318,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130754985</v>
+        <v>130789470</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,14 +2356,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490434</v>
+        <v>490376</v>
       </c>
       <c r="R17" t="n">
-        <v>6764045</v>
+        <v>6763596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,7 +2395,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2400,7 +2405,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,28 +2414,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130754896</v>
+        <v>130789473</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,14 +2464,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490446</v>
+        <v>490444</v>
       </c>
       <c r="R18" t="n">
-        <v>6764008</v>
+        <v>6763969</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2503,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2507,7 +2513,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,28 +2522,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130757159</v>
+        <v>130757425</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2569,7 +2576,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490482</v>
+        <v>490361</v>
       </c>
       <c r="R19" t="n">
         <v>6763574</v>
@@ -2634,17 +2641,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130754796</v>
+        <v>130754307</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2676,10 +2683,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490463</v>
+        <v>490501</v>
       </c>
       <c r="R20" t="n">
-        <v>6763939</v>
+        <v>6763773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2741,17 +2748,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130755667</v>
+        <v>130757199</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,39 +2766,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490444</v>
+        <v>490467</v>
       </c>
       <c r="R21" t="n">
-        <v>6763770</v>
+        <v>6763573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2825,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,12 +2835,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,57 +2855,52 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130757236</v>
+        <v>130789474</v>
       </c>
       <c r="B22" t="n">
-        <v>5177</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490467</v>
+        <v>490445</v>
       </c>
       <c r="R22" t="n">
-        <v>6763573</v>
+        <v>6763972</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2940,7 +2932,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2950,7 +2942,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2959,68 +2951,64 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130757715</v>
+        <v>130755955</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490186</v>
+        <v>490486</v>
       </c>
       <c r="R23" t="n">
-        <v>6763602</v>
+        <v>6763627</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3052,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3062,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,57 +3070,52 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130757247</v>
+        <v>130789495</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490467</v>
+        <v>490496</v>
       </c>
       <c r="R24" t="n">
-        <v>6763573</v>
+        <v>6763849</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3164,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3174,7 +3157,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,28 +3166,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130754851</v>
+        <v>130754985</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,14 +3216,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490449</v>
+        <v>490434</v>
       </c>
       <c r="R25" t="n">
-        <v>6763949</v>
+        <v>6764045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3284,11 +3268,6 @@
           <t>11:43</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3306,17 +3285,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130757412</v>
+        <v>130754896</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,14 +3323,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490381</v>
+        <v>490446</v>
       </c>
       <c r="R26" t="n">
-        <v>6763583</v>
+        <v>6764008</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3383,7 +3362,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,7 +3372,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3413,17 +3392,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755409</v>
+        <v>130757159</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3451,14 +3430,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490447</v>
+        <v>490482</v>
       </c>
       <c r="R27" t="n">
-        <v>6763817</v>
+        <v>6763574</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3490,7 +3469,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3500,7 +3479,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3520,17 +3499,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755062</v>
+        <v>130755667</v>
       </c>
       <c r="B28" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,7 +3537,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3567,10 +3546,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490434</v>
+        <v>490444</v>
       </c>
       <c r="R28" t="n">
-        <v>6764045</v>
+        <v>6763770</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3596,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,17 +3616,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130757564</v>
+        <v>130789472</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,14 +3654,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490230</v>
+        <v>490450</v>
       </c>
       <c r="R29" t="n">
-        <v>6763582</v>
+        <v>6763926</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3714,7 +3693,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3724,7 +3703,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,28 +3712,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130754014</v>
+        <v>130754796</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,10 +3766,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490548</v>
+        <v>490463</v>
       </c>
       <c r="R30" t="n">
-        <v>6763654</v>
+        <v>6763939</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3851,52 +3831,57 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130754953</v>
+        <v>130757715</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490440</v>
+        <v>490186</v>
       </c>
       <c r="R31" t="n">
-        <v>6764028</v>
+        <v>6763602</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3928,7 +3913,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3938,12 +3923,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,57 +3943,52 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130758028</v>
+        <v>130789476</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490175</v>
+        <v>490438</v>
       </c>
       <c r="R32" t="n">
-        <v>6763613</v>
+        <v>6764018</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,7 +4020,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4055,7 +4030,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4064,28 +4039,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130758032</v>
+        <v>130789475</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4113,14 +4089,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490175</v>
+        <v>490441</v>
       </c>
       <c r="R33" t="n">
-        <v>6763613</v>
+        <v>6763984</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4152,7 +4128,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4162,7 +4138,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4171,56 +4147,57 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130758572</v>
+        <v>130757236</v>
       </c>
       <c r="B34" t="n">
-        <v>57851</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4229,10 +4206,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490494</v>
+        <v>490467</v>
       </c>
       <c r="R34" t="n">
-        <v>6763540</v>
+        <v>6763573</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4294,57 +4271,52 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130755323</v>
+        <v>130754851</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490451</v>
+        <v>490449</v>
       </c>
       <c r="R35" t="n">
-        <v>6763833</v>
+        <v>6763949</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4389,6 +4361,11 @@
           <t>11:43</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4406,17 +4383,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130789469</v>
+        <v>130757412</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4448,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490373</v>
+        <v>490381</v>
       </c>
       <c r="R36" t="n">
-        <v>6763590</v>
+        <v>6763583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4483,7 +4460,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4493,7 +4470,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,29 +4479,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130789471</v>
+        <v>130789468</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,10 +4532,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490498</v>
+        <v>490321</v>
       </c>
       <c r="R37" t="n">
-        <v>6763669</v>
+        <v>6763593</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4591,7 +4567,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4601,7 +4577,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4629,45 +4605,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130789490</v>
+        <v>130757247</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>5197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490470</v>
+        <v>490467</v>
       </c>
       <c r="R38" t="n">
-        <v>6763909</v>
+        <v>6763573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,7 +4680,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4709,7 +4690,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4718,29 +4699,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130789477</v>
+        <v>130789489</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4772,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490435</v>
+        <v>490467</v>
       </c>
       <c r="R39" t="n">
-        <v>6764047</v>
+        <v>6763913</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4807,7 +4787,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4817,7 +4797,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4845,10 +4825,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130789496</v>
+        <v>130789487</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4880,10 +4860,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490526</v>
+        <v>490472</v>
       </c>
       <c r="R40" t="n">
-        <v>6763737</v>
+        <v>6763924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,7 +4895,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4925,7 +4905,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4953,10 +4933,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130789482</v>
+        <v>130789497</v>
       </c>
       <c r="B41" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4988,10 +4968,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490451</v>
+        <v>490525</v>
       </c>
       <c r="R41" t="n">
-        <v>6764011</v>
+        <v>6763706</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5023,7 +5003,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5033,7 +5013,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5061,10 +5041,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130789470</v>
+        <v>130755409</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,14 +5072,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490376</v>
+        <v>490447</v>
       </c>
       <c r="R42" t="n">
-        <v>6763596</v>
+        <v>6763817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5131,7 +5111,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5141,7 +5121,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5150,29 +5130,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130789473</v>
+        <v>130755062</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5180,34 +5159,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490444</v>
+        <v>490434</v>
       </c>
       <c r="R43" t="n">
-        <v>6763969</v>
+        <v>6764045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,7 +5223,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5249,7 +5233,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5258,29 +5247,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130789474</v>
+        <v>130757564</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5308,14 +5296,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490445</v>
+        <v>490230</v>
       </c>
       <c r="R44" t="n">
-        <v>6763972</v>
+        <v>6763582</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5347,7 +5335,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5357,7 +5345,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5366,64 +5354,68 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130789495</v>
+        <v>130758028</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490496</v>
+        <v>490175</v>
       </c>
       <c r="R45" t="n">
-        <v>6763849</v>
+        <v>6763613</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5455,7 +5447,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5465,7 +5457,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5474,29 +5466,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130789472</v>
+        <v>130754014</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5528,10 +5519,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490450</v>
+        <v>490548</v>
       </c>
       <c r="R46" t="n">
-        <v>6763926</v>
+        <v>6763654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5563,7 +5554,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5573,7 +5564,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5582,29 +5573,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130789476</v>
+        <v>130754953</v>
       </c>
       <c r="B47" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5632,14 +5622,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490438</v>
+        <v>490440</v>
       </c>
       <c r="R47" t="n">
-        <v>6764018</v>
+        <v>6764028</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5671,7 +5661,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5681,7 +5671,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5690,29 +5685,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130789475</v>
+        <v>130789459</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5744,10 +5738,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490441</v>
+        <v>490499</v>
       </c>
       <c r="R48" t="n">
-        <v>6763984</v>
+        <v>6763662</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5779,7 +5773,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5789,7 +5783,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5817,10 +5816,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130789468</v>
+        <v>130758032</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5848,14 +5847,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490321</v>
+        <v>490175</v>
       </c>
       <c r="R49" t="n">
-        <v>6763593</v>
+        <v>6763613</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5887,7 +5886,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5897,7 +5896,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5906,29 +5905,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130789489</v>
+        <v>130758572</v>
       </c>
       <c r="B50" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5936,34 +5934,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490467</v>
+        <v>490494</v>
       </c>
       <c r="R50" t="n">
-        <v>6763913</v>
+        <v>6763540</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5995,7 +5998,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6005,7 +6008,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6014,29 +6017,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130789487</v>
+        <v>130789491</v>
       </c>
       <c r="B51" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6068,10 +6070,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490472</v>
+        <v>490481</v>
       </c>
       <c r="R51" t="n">
-        <v>6763924</v>
+        <v>6763891</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6103,7 +6105,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6113,7 +6115,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6141,10 +6143,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130789497</v>
+        <v>130789493</v>
       </c>
       <c r="B52" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6176,10 +6178,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490525</v>
+        <v>490482</v>
       </c>
       <c r="R52" t="n">
-        <v>6763706</v>
+        <v>6763883</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6211,7 +6213,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6221,7 +6223,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6249,10 +6251,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130789459</v>
+        <v>130789498</v>
       </c>
       <c r="B53" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6284,10 +6286,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490499</v>
+        <v>490523</v>
       </c>
       <c r="R53" t="n">
-        <v>6763662</v>
+        <v>6763700</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6319,7 +6321,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6329,12 +6331,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>vid gran 250 år plus</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6362,10 +6359,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130789491</v>
+        <v>130789492</v>
       </c>
       <c r="B54" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6400,7 +6397,7 @@
         <v>490481</v>
       </c>
       <c r="R54" t="n">
-        <v>6763891</v>
+        <v>6763889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6432,7 +6429,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6442,7 +6439,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6470,10 +6467,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130789493</v>
+        <v>130789494</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6505,10 +6502,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490482</v>
+        <v>490480</v>
       </c>
       <c r="R55" t="n">
-        <v>6763883</v>
+        <v>6763872</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6540,7 +6537,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6550,7 +6547,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6578,45 +6575,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130789498</v>
+        <v>130755323</v>
       </c>
       <c r="B56" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490523</v>
+        <v>490451</v>
       </c>
       <c r="R56" t="n">
-        <v>6763700</v>
+        <v>6763833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6648,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6658,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6667,238 +6669,21 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>130789492</v>
-      </c>
-      <c r="B57" t="n">
-        <v>79211</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Kråkbackarna, Dlr</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>490481</v>
-      </c>
-      <c r="R57" t="n">
-        <v>6763889</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Bo karlstens, Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>130789494</v>
-      </c>
-      <c r="B58" t="n">
-        <v>79211</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Kråkbackarna, Dlr</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>490480</v>
-      </c>
-      <c r="R58" t="n">
-        <v>6763872</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Bo karlstens, Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,7 +790,7 @@
         <v>130789469</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>130754287</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>130789471</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>130758328</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>130789490</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>130755448</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>130789477</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>130789496</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>130789482</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>130758082</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>130754257</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130757152</v>
+        <v>130754083</v>
       </c>
       <c r="B15" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,39 +2103,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490482</v>
+        <v>490529</v>
       </c>
       <c r="R15" t="n">
-        <v>6763574</v>
+        <v>6763665</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2177,12 +2175,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, tall med gran till vänster</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,6 +2189,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130754083</v>
+        <v>130789470</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,19 +2237,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490529</v>
+        <v>490376</v>
       </c>
       <c r="R16" t="n">
-        <v>6763665</v>
+        <v>6763596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2292,12 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bild, tall med gran till vänster</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,22 +2304,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130789470</v>
+        <v>130757152</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,34 +2327,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490376</v>
+        <v>490482</v>
       </c>
       <c r="R17" t="n">
-        <v>6763596</v>
+        <v>6763574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2391,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,7 +2401,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,19 +2415,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2436,7 +2436,7 @@
         <v>130789473</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>130757425</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>130754307</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>130757199</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>130789474</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>130755955</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>130789495</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>130754985</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>130754896</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130757159</v>
+        <v>130755667</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,34 +3410,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490482</v>
+        <v>490444</v>
       </c>
       <c r="R27" t="n">
-        <v>6763574</v>
+        <v>6763770</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3474,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3479,7 +3484,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3506,10 +3516,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130755667</v>
+        <v>130757159</v>
       </c>
       <c r="B28" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3517,39 +3527,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490444</v>
+        <v>490482</v>
       </c>
       <c r="R28" t="n">
-        <v>6763770</v>
+        <v>6763574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3581,7 +3586,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3591,12 +3596,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3626,7 +3626,7 @@
         <v>130789472</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>130754796</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,50 +3838,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130757715</v>
+        <v>130789476</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490186</v>
+        <v>490438</v>
       </c>
       <c r="R31" t="n">
-        <v>6763602</v>
+        <v>6764018</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3908,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3923,7 +3918,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,28 +3927,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130789476</v>
+        <v>130789475</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3985,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490438</v>
+        <v>490441</v>
       </c>
       <c r="R32" t="n">
-        <v>6764018</v>
+        <v>6763984</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4020,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4030,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4058,45 +4054,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130789475</v>
+        <v>130757236</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490441</v>
+        <v>490467</v>
       </c>
       <c r="R33" t="n">
-        <v>6763984</v>
+        <v>6763573</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4128,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4138,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,29 +4148,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130757236</v>
+        <v>130757715</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4202,14 +4202,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490467</v>
+        <v>490186</v>
       </c>
       <c r="R34" t="n">
-        <v>6763573</v>
+        <v>6763602</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4278,45 +4278,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130754851</v>
+        <v>130757247</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>5197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490449</v>
+        <v>490467</v>
       </c>
       <c r="R35" t="n">
-        <v>6763949</v>
+        <v>6763573</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4348,7 +4353,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4358,12 +4363,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,10 +4390,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130757412</v>
+        <v>130754851</v>
       </c>
       <c r="B36" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490381</v>
+        <v>490449</v>
       </c>
       <c r="R36" t="n">
-        <v>6763583</v>
+        <v>6763949</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4470,7 +4470,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4497,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130789468</v>
+        <v>130757412</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4532,10 +4537,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490321</v>
+        <v>490381</v>
       </c>
       <c r="R37" t="n">
-        <v>6763593</v>
+        <v>6763583</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,7 +4572,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4577,7 +4582,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,69 +4591,63 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130757247</v>
+        <v>130789468</v>
       </c>
       <c r="B38" t="n">
-        <v>5197</v>
+        <v>79220</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490467</v>
+        <v>490321</v>
       </c>
       <c r="R38" t="n">
-        <v>6763573</v>
+        <v>6763593</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,7 +4679,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4690,7 +4689,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4699,28 +4698,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130789489</v>
+        <v>130755062</v>
       </c>
       <c r="B39" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490467</v>
+        <v>490434</v>
       </c>
       <c r="R39" t="n">
-        <v>6763913</v>
+        <v>6764045</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4787,7 +4792,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4797,7 +4802,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4806,29 +4816,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130789487</v>
+        <v>130789489</v>
       </c>
       <c r="B40" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4860,10 +4869,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490472</v>
+        <v>490467</v>
       </c>
       <c r="R40" t="n">
-        <v>6763924</v>
+        <v>6763913</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,7 +4904,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4905,7 +4914,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4933,10 +4942,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130789497</v>
+        <v>130789487</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4968,10 +4977,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490525</v>
+        <v>490472</v>
       </c>
       <c r="R41" t="n">
-        <v>6763706</v>
+        <v>6763924</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,7 +5012,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5013,7 +5022,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,10 +5050,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755409</v>
+        <v>130789497</v>
       </c>
       <c r="B42" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5072,14 +5081,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490447</v>
+        <v>490525</v>
       </c>
       <c r="R42" t="n">
-        <v>6763817</v>
+        <v>6763706</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5111,7 +5120,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5121,7 +5130,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5130,28 +5139,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130755062</v>
+        <v>130755409</v>
       </c>
       <c r="B43" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5159,39 +5169,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490434</v>
+        <v>490447</v>
       </c>
       <c r="R43" t="n">
-        <v>6764045</v>
+        <v>6763817</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5234,11 +5239,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5268,7 +5268,7 @@
         <v>130757564</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5372,50 +5372,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130758028</v>
+        <v>130754014</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>79220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490175</v>
+        <v>490548</v>
       </c>
       <c r="R45" t="n">
-        <v>6763613</v>
+        <v>6763654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5447,7 +5442,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5457,7 +5452,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5484,10 +5479,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130754014</v>
+        <v>130754953</v>
       </c>
       <c r="B46" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5515,14 +5510,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490548</v>
+        <v>490440</v>
       </c>
       <c r="R46" t="n">
-        <v>6763654</v>
+        <v>6764028</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5565,6 +5560,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5591,45 +5591,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130754953</v>
+        <v>130758028</v>
       </c>
       <c r="B47" t="n">
-        <v>79219</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490440</v>
+        <v>490175</v>
       </c>
       <c r="R47" t="n">
-        <v>6764028</v>
+        <v>6763613</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5661,7 +5666,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5671,12 +5676,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5706,7 +5706,7 @@
         <v>130789459</v>
       </c>
       <c r="B48" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>130758032</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>130758572</v>
       </c>
       <c r="B50" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>130789491</v>
       </c>
       <c r="B51" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>130789493</v>
       </c>
       <c r="B52" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>130789498</v>
       </c>
       <c r="B53" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>130789492</v>
       </c>
       <c r="B54" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>130789494</v>
       </c>
       <c r="B55" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6685,6 +6685,347 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130817408</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>490315</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6763623</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130816918</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>490472</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6763537</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2 bilder på gran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130817398</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57863</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>490315</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6763623</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>3 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130789469</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130754287</v>
+        <v>130789471</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,39 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490501</v>
+        <v>490498</v>
       </c>
       <c r="R4" t="n">
-        <v>6763773</v>
+        <v>6763669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,28 +984,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130789471</v>
+        <v>130754287</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,34 +1014,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490498</v>
+        <v>490501</v>
       </c>
       <c r="R5" t="n">
-        <v>6763669</v>
+        <v>6763773</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1087,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,19 +1097,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         <v>130758328</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130789490</v>
+        <v>130755448</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1253,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490470</v>
+        <v>490441</v>
       </c>
       <c r="R7" t="n">
-        <v>6763909</v>
+        <v>6763800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,29 +1311,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755448</v>
+        <v>130789490</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,14 +1360,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490441</v>
+        <v>490470</v>
       </c>
       <c r="R8" t="n">
-        <v>6763800</v>
+        <v>6763909</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,7 +1399,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1409,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,28 +1418,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130789477</v>
+        <v>130789496</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490435</v>
+        <v>490526</v>
       </c>
       <c r="R9" t="n">
-        <v>6764047</v>
+        <v>6763737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130789496</v>
+        <v>130789482</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490526</v>
+        <v>490451</v>
       </c>
       <c r="R10" t="n">
-        <v>6763737</v>
+        <v>6764011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130789482</v>
+        <v>130789477</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490451</v>
+        <v>490435</v>
       </c>
       <c r="R11" t="n">
-        <v>6764011</v>
+        <v>6764047</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,50 +1761,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130757655</v>
+        <v>130758082</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490214</v>
+        <v>490186</v>
       </c>
       <c r="R12" t="n">
-        <v>6763590</v>
+        <v>6763602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,45 +1868,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130758082</v>
+        <v>130757655</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490186</v>
+        <v>490214</v>
       </c>
       <c r="R13" t="n">
-        <v>6763602</v>
+        <v>6763590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +1983,7 @@
         <v>130754257</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130754083</v>
+        <v>130757152</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,37 +2103,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490529</v>
+        <v>490482</v>
       </c>
       <c r="R15" t="n">
-        <v>6763665</v>
+        <v>6763574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2167,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,12 +2177,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 bild, tall med gran till vänster</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2191,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>130789470</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,10 +2317,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130757152</v>
+        <v>130754083</v>
       </c>
       <c r="B17" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,39 +2328,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490482</v>
+        <v>490529</v>
       </c>
       <c r="R17" t="n">
-        <v>6763574</v>
+        <v>6763665</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2401,12 +2400,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild, tall med gran till vänster</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,6 +2414,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130789473</v>
+        <v>130757199</v>
       </c>
       <c r="B18" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490444</v>
+        <v>490467</v>
       </c>
       <c r="R18" t="n">
-        <v>6763969</v>
+        <v>6763573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,19 +2522,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2544,7 +2543,7 @@
         <v>130757425</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2650,7 @@
         <v>130754307</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2755,10 +2754,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130757199</v>
+        <v>130789473</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490467</v>
+        <v>490444</v>
       </c>
       <c r="R21" t="n">
-        <v>6763573</v>
+        <v>6763969</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,7 +2824,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2835,7 +2834,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,18 +2843,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         <v>130789474</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>130755955</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130789495</v>
+        <v>130754896</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,14 +3108,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490496</v>
+        <v>490446</v>
       </c>
       <c r="R24" t="n">
-        <v>6763849</v>
+        <v>6764008</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,19 +3166,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3188,7 +3187,7 @@
         <v>130754985</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130754896</v>
+        <v>130789495</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,14 +3322,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490446</v>
+        <v>490496</v>
       </c>
       <c r="R26" t="n">
-        <v>6764008</v>
+        <v>6763849</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,7 +3361,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3372,7 +3371,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3381,28 +3380,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130755667</v>
+        <v>130757159</v>
       </c>
       <c r="B27" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,39 +3410,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490444</v>
+        <v>490482</v>
       </c>
       <c r="R27" t="n">
-        <v>6763770</v>
+        <v>6763574</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,7 +3469,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3484,12 +3479,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3516,10 +3506,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130757159</v>
+        <v>130789472</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490482</v>
+        <v>490450</v>
       </c>
       <c r="R28" t="n">
-        <v>6763574</v>
+        <v>6763926</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3586,7 +3576,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3596,7 +3586,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3605,28 +3595,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130789472</v>
+        <v>130754796</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490450</v>
+        <v>490463</v>
       </c>
       <c r="R29" t="n">
-        <v>6763926</v>
+        <v>6763939</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3693,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3703,7 +3694,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3712,29 +3703,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130754796</v>
+        <v>130755667</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3742,34 +3732,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490463</v>
+        <v>490444</v>
       </c>
       <c r="R30" t="n">
-        <v>6763939</v>
+        <v>6763770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,6 +3807,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,45 +3838,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130789476</v>
+        <v>130757236</v>
       </c>
       <c r="B31" t="n">
-        <v>79220</v>
+        <v>5177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490438</v>
+        <v>490467</v>
       </c>
       <c r="R31" t="n">
-        <v>6764018</v>
+        <v>6763573</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3908,7 +3913,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3918,7 +3923,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3927,64 +3932,68 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130789475</v>
+        <v>130757715</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490441</v>
+        <v>490186</v>
       </c>
       <c r="R32" t="n">
-        <v>6763984</v>
+        <v>6763602</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4025,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4035,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4035,69 +4044,63 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130757236</v>
+        <v>130789475</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490467</v>
+        <v>490441</v>
       </c>
       <c r="R33" t="n">
-        <v>6763573</v>
+        <v>6763984</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4129,7 +4132,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4139,7 +4142,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,68 +4151,64 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130757715</v>
+        <v>130789476</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490186</v>
+        <v>490438</v>
       </c>
       <c r="R34" t="n">
-        <v>6763602</v>
+        <v>6764018</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,7 +4240,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4251,7 +4250,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,68 +4259,64 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130757247</v>
+        <v>130789468</v>
       </c>
       <c r="B35" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490467</v>
+        <v>490321</v>
       </c>
       <c r="R35" t="n">
-        <v>6763573</v>
+        <v>6763593</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4353,7 +4348,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4363,7 +4358,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4372,18 +4367,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4393,7 +4389,7 @@
         <v>130754851</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4505,7 +4501,7 @@
         <v>130757412</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4609,45 +4605,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130789468</v>
+        <v>130757247</v>
       </c>
       <c r="B38" t="n">
-        <v>79220</v>
+        <v>5197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490321</v>
+        <v>490467</v>
       </c>
       <c r="R38" t="n">
-        <v>6763593</v>
+        <v>6763573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4680,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4689,7 +4690,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4698,29 +4699,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130755062</v>
+        <v>130789497</v>
       </c>
       <c r="B39" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490434</v>
+        <v>490525</v>
       </c>
       <c r="R39" t="n">
-        <v>6764045</v>
+        <v>6763706</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4792,7 +4787,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4802,12 +4797,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4816,28 +4806,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130789489</v>
+        <v>130789487</v>
       </c>
       <c r="B40" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,10 +4860,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490467</v>
+        <v>490472</v>
       </c>
       <c r="R40" t="n">
-        <v>6763913</v>
+        <v>6763924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,7 +4895,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4914,7 +4905,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4942,10 +4933,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130789487</v>
+        <v>130757564</v>
       </c>
       <c r="B41" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4973,14 +4964,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490472</v>
+        <v>490230</v>
       </c>
       <c r="R41" t="n">
-        <v>6763924</v>
+        <v>6763582</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5012,7 +5003,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5022,7 +5013,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5031,29 +5022,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130789497</v>
+        <v>130789489</v>
       </c>
       <c r="B42" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5085,10 +5075,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490525</v>
+        <v>490467</v>
       </c>
       <c r="R42" t="n">
-        <v>6763706</v>
+        <v>6763913</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5120,7 +5110,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5130,7 +5120,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5161,7 +5151,7 @@
         <v>130755409</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5265,10 +5255,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130757564</v>
+        <v>130755062</v>
       </c>
       <c r="B44" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5276,34 +5266,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490230</v>
+        <v>490434</v>
       </c>
       <c r="R44" t="n">
-        <v>6763582</v>
+        <v>6764045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5335,7 +5330,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5345,7 +5340,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,10 +5372,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130754014</v>
+        <v>130754953</v>
       </c>
       <c r="B45" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5403,14 +5403,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490548</v>
+        <v>490440</v>
       </c>
       <c r="R45" t="n">
-        <v>6763654</v>
+        <v>6764028</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5453,6 +5453,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,10 +5484,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130754953</v>
+        <v>130754014</v>
       </c>
       <c r="B46" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5510,14 +5515,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490440</v>
+        <v>490548</v>
       </c>
       <c r="R46" t="n">
-        <v>6764028</v>
+        <v>6763654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5560,11 +5565,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130789459</v>
+        <v>130758032</v>
       </c>
       <c r="B48" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5734,14 +5734,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490499</v>
+        <v>490175</v>
       </c>
       <c r="R48" t="n">
-        <v>6763662</v>
+        <v>6763613</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5783,12 +5783,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>vid gran 250 år plus</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5797,29 +5792,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130758032</v>
+        <v>130789459</v>
       </c>
       <c r="B49" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5847,14 +5841,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490175</v>
+        <v>490499</v>
       </c>
       <c r="R49" t="n">
-        <v>6763613</v>
+        <v>6763662</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5886,7 +5880,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5896,7 +5890,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5905,18 +5904,19 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5926,7 +5926,7 @@
         <v>130758572</v>
       </c>
       <c r="B50" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130789491</v>
+        <v>130789492</v>
       </c>
       <c r="B51" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>490481</v>
       </c>
       <c r="R51" t="n">
-        <v>6763891</v>
+        <v>6763889</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6146,7 +6146,7 @@
         <v>130789493</v>
       </c>
       <c r="B52" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>130789498</v>
       </c>
       <c r="B53" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6359,10 +6359,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130789492</v>
+        <v>130789491</v>
       </c>
       <c r="B54" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>490481</v>
       </c>
       <c r="R54" t="n">
-        <v>6763889</v>
+        <v>6763891</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6470,7 +6470,7 @@
         <v>130789494</v>
       </c>
       <c r="B55" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>130817408</v>
       </c>
       <c r="B57" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>130816918</v>
       </c>
       <c r="B58" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>130817398</v>
       </c>
       <c r="B59" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -2092,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130757152</v>
+        <v>130789470</v>
       </c>
       <c r="B15" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,39 +2103,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490482</v>
+        <v>490376</v>
       </c>
       <c r="R15" t="n">
-        <v>6763574</v>
+        <v>6763596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2162,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2177,12 +2172,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,25 +2181,26 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130789470</v>
+        <v>130754083</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2238,16 +2229,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490376</v>
+        <v>490529</v>
       </c>
       <c r="R16" t="n">
-        <v>6763596</v>
+        <v>6763665</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2289,7 +2283,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bild, tall med gran till vänster</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,22 +2304,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130754083</v>
+        <v>130757152</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,37 +2327,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490529</v>
+        <v>490482</v>
       </c>
       <c r="R17" t="n">
-        <v>6763665</v>
+        <v>6763574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,7 +2391,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2400,12 +2401,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bild, tall med gran till vänster</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,7 +2415,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -5372,45 +5372,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130754953</v>
+        <v>130758028</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490440</v>
+        <v>490175</v>
       </c>
       <c r="R45" t="n">
-        <v>6764028</v>
+        <v>6763613</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5442,7 +5447,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5452,12 +5457,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5484,7 +5484,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130754014</v>
+        <v>130754953</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5515,14 +5515,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490548</v>
+        <v>490440</v>
       </c>
       <c r="R46" t="n">
-        <v>6763654</v>
+        <v>6764028</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5565,6 +5565,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5591,50 +5596,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130758028</v>
+        <v>130754014</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490175</v>
+        <v>490548</v>
       </c>
       <c r="R47" t="n">
-        <v>6763613</v>
+        <v>6763654</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130758032</v>
+        <v>130758572</v>
       </c>
       <c r="B48" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5714,34 +5714,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490175</v>
+        <v>490494</v>
       </c>
       <c r="R48" t="n">
-        <v>6763613</v>
+        <v>6763540</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5810,7 +5815,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130789459</v>
+        <v>130758032</v>
       </c>
       <c r="B49" t="n">
         <v>79221</v>
@@ -5841,14 +5846,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490499</v>
+        <v>490175</v>
       </c>
       <c r="R49" t="n">
-        <v>6763662</v>
+        <v>6763613</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5880,7 +5885,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5890,12 +5895,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>vid gran 250 år plus</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5904,29 +5904,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130758572</v>
+        <v>130789459</v>
       </c>
       <c r="B50" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,39 +5933,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490494</v>
+        <v>490499</v>
       </c>
       <c r="R50" t="n">
-        <v>6763540</v>
+        <v>6763662</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,7 +5992,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6008,7 +6002,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,18 +6016,19 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130755448</v>
+        <v>130789490</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1253,14 +1253,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490441</v>
+        <v>490470</v>
       </c>
       <c r="R7" t="n">
-        <v>6763800</v>
+        <v>6763909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,25 +1311,26 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130789490</v>
+        <v>130755448</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1360,14 +1361,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490470</v>
+        <v>490441</v>
       </c>
       <c r="R8" t="n">
-        <v>6763909</v>
+        <v>6763800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1409,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,26 +1419,25 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130789496</v>
+        <v>130789477</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490526</v>
+        <v>490435</v>
       </c>
       <c r="R9" t="n">
-        <v>6763737</v>
+        <v>6764047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130789482</v>
+        <v>130789496</v>
       </c>
       <c r="B10" t="n">
         <v>79221</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490451</v>
+        <v>490526</v>
       </c>
       <c r="R10" t="n">
-        <v>6764011</v>
+        <v>6763737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130789477</v>
+        <v>130789482</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490435</v>
+        <v>490451</v>
       </c>
       <c r="R11" t="n">
-        <v>6764047</v>
+        <v>6764011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2092,7 +2092,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130789470</v>
+        <v>130754083</v>
       </c>
       <c r="B15" t="n">
         <v>79221</v>
@@ -2121,16 +2121,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490376</v>
+        <v>490529</v>
       </c>
       <c r="R15" t="n">
-        <v>6763596</v>
+        <v>6763665</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2172,7 +2175,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 bild, tall med gran till vänster</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,19 +2196,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130754083</v>
+        <v>130789470</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2229,19 +2237,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490529</v>
+        <v>490376</v>
       </c>
       <c r="R16" t="n">
-        <v>6763665</v>
+        <v>6763596</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,12 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bild, tall med gran till vänster</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,12 +2304,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130757199</v>
+        <v>130789473</v>
       </c>
       <c r="B18" t="n">
         <v>79221</v>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490467</v>
+        <v>490444</v>
       </c>
       <c r="R18" t="n">
-        <v>6763573</v>
+        <v>6763969</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,18 +2522,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2754,7 +2755,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130789473</v>
+        <v>130757199</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -2789,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490444</v>
+        <v>490467</v>
       </c>
       <c r="R21" t="n">
-        <v>6763969</v>
+        <v>6763573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,7 +2825,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2834,7 +2835,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,19 +2844,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130754896</v>
+        <v>130789495</v>
       </c>
       <c r="B24" t="n">
         <v>79221</v>
@@ -3108,14 +3108,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490446</v>
+        <v>490496</v>
       </c>
       <c r="R24" t="n">
-        <v>6764008</v>
+        <v>6763849</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,18 +3166,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3291,7 +3292,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130789495</v>
+        <v>130754896</v>
       </c>
       <c r="B26" t="n">
         <v>79221</v>
@@ -3322,14 +3323,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490496</v>
+        <v>490446</v>
       </c>
       <c r="R26" t="n">
-        <v>6763849</v>
+        <v>6764008</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,7 +3362,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3371,7 +3372,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3380,19 +3381,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3838,50 +3838,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130757236</v>
+        <v>130789476</v>
       </c>
       <c r="B31" t="n">
-        <v>5177</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490467</v>
+        <v>490438</v>
       </c>
       <c r="R31" t="n">
-        <v>6763573</v>
+        <v>6764018</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3908,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3923,7 +3918,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,68 +3927,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130757715</v>
+        <v>130789475</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490186</v>
+        <v>490441</v>
       </c>
       <c r="R32" t="n">
-        <v>6763602</v>
+        <v>6763984</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4035,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,63 +4035,69 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130789475</v>
+        <v>130757236</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490441</v>
+        <v>490467</v>
       </c>
       <c r="R33" t="n">
-        <v>6763984</v>
+        <v>6763573</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4132,7 +4129,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4142,7 +4139,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4151,64 +4148,68 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130789476</v>
+        <v>130757715</v>
       </c>
       <c r="B34" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490438</v>
+        <v>490186</v>
       </c>
       <c r="R34" t="n">
-        <v>6764018</v>
+        <v>6763602</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4240,7 +4241,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4250,7 +4251,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,26 +4260,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130789468</v>
+        <v>130754851</v>
       </c>
       <c r="B35" t="n">
         <v>79221</v>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490321</v>
+        <v>490449</v>
       </c>
       <c r="R35" t="n">
-        <v>6763593</v>
+        <v>6763949</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4358,7 +4358,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4367,26 +4372,25 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130754851</v>
+        <v>130757412</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490449</v>
+        <v>490381</v>
       </c>
       <c r="R36" t="n">
-        <v>6763949</v>
+        <v>6763583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4456,7 +4460,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4466,12 +4470,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4498,7 +4497,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130757412</v>
+        <v>130789468</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4533,10 +4532,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490381</v>
+        <v>490321</v>
       </c>
       <c r="R37" t="n">
-        <v>6763583</v>
+        <v>6763593</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4568,7 +4567,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4578,7 +4577,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4587,18 +4586,19 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130789497</v>
+        <v>130789489</v>
       </c>
       <c r="B39" t="n">
         <v>79221</v>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490525</v>
+        <v>490467</v>
       </c>
       <c r="R39" t="n">
-        <v>6763706</v>
+        <v>6763913</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4933,7 +4933,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130757564</v>
+        <v>130789497</v>
       </c>
       <c r="B41" t="n">
         <v>79221</v>
@@ -4964,14 +4964,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490230</v>
+        <v>490525</v>
       </c>
       <c r="R41" t="n">
-        <v>6763582</v>
+        <v>6763706</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,25 +5022,26 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130789489</v>
+        <v>130755409</v>
       </c>
       <c r="B42" t="n">
         <v>79221</v>
@@ -5071,14 +5072,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490467</v>
+        <v>490447</v>
       </c>
       <c r="R42" t="n">
-        <v>6763913</v>
+        <v>6763817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5110,7 +5111,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5120,7 +5121,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5129,26 +5130,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130755409</v>
+        <v>130757564</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5179,14 +5179,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490447</v>
+        <v>490230</v>
       </c>
       <c r="R43" t="n">
-        <v>6763817</v>
+        <v>6763582</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5372,50 +5372,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130758028</v>
+        <v>130754014</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490175</v>
+        <v>490548</v>
       </c>
       <c r="R45" t="n">
-        <v>6763613</v>
+        <v>6763654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5447,7 +5442,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5457,7 +5452,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5596,45 +5591,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130754014</v>
+        <v>130758028</v>
       </c>
       <c r="B47" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490548</v>
+        <v>490175</v>
       </c>
       <c r="R47" t="n">
-        <v>6763654</v>
+        <v>6763613</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5815,7 +5815,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130758032</v>
+        <v>130789459</v>
       </c>
       <c r="B49" t="n">
         <v>79221</v>
@@ -5846,14 +5846,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490175</v>
+        <v>490499</v>
       </c>
       <c r="R49" t="n">
-        <v>6763613</v>
+        <v>6763662</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5895,7 +5895,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5904,25 +5909,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130789459</v>
+        <v>130758032</v>
       </c>
       <c r="B50" t="n">
         <v>79221</v>
@@ -5953,14 +5959,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490499</v>
+        <v>490175</v>
       </c>
       <c r="R50" t="n">
-        <v>6763662</v>
+        <v>6763613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5992,7 +5998,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6002,12 +6008,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>vid gran 250 år plus</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6016,26 +6017,25 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130789492</v>
+        <v>130789491</v>
       </c>
       <c r="B51" t="n">
         <v>79221</v>
@@ -6073,7 +6073,7 @@
         <v>490481</v>
       </c>
       <c r="R51" t="n">
-        <v>6763889</v>
+        <v>6763891</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6359,7 +6359,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130789491</v>
+        <v>130789492</v>
       </c>
       <c r="B54" t="n">
         <v>79221</v>
@@ -6397,7 +6397,7 @@
         <v>490481</v>
       </c>
       <c r="R54" t="n">
-        <v>6763891</v>
+        <v>6763889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6467,45 +6467,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130789494</v>
+        <v>130755323</v>
       </c>
       <c r="B55" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490480</v>
+        <v>490451</v>
       </c>
       <c r="R55" t="n">
-        <v>6763872</v>
+        <v>6763833</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6537,7 +6542,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6547,7 +6552,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6556,69 +6561,63 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130755323</v>
+        <v>130789494</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490451</v>
+        <v>490480</v>
       </c>
       <c r="R56" t="n">
-        <v>6763833</v>
+        <v>6763872</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6650,7 +6649,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6660,7 +6659,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6669,18 +6668,19 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -4278,45 +4278,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130754851</v>
+        <v>130757247</v>
       </c>
       <c r="B35" t="n">
-        <v>79221</v>
+        <v>5197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490449</v>
+        <v>490467</v>
       </c>
       <c r="R35" t="n">
-        <v>6763949</v>
+        <v>6763573</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4348,7 +4353,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4358,12 +4363,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130757412</v>
+        <v>130754851</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490381</v>
+        <v>490449</v>
       </c>
       <c r="R36" t="n">
-        <v>6763583</v>
+        <v>6763949</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4470,7 +4470,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4497,7 +4502,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130789468</v>
+        <v>130757412</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4532,10 +4537,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490321</v>
+        <v>490381</v>
       </c>
       <c r="R37" t="n">
-        <v>6763593</v>
+        <v>6763583</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,7 +4572,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4577,7 +4582,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,69 +4591,63 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130757247</v>
+        <v>130789468</v>
       </c>
       <c r="B38" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490467</v>
+        <v>490321</v>
       </c>
       <c r="R38" t="n">
-        <v>6763573</v>
+        <v>6763593</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,7 +4679,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4690,7 +4689,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4699,18 +4698,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -6467,50 +6467,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130755323</v>
+        <v>130789494</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490451</v>
+        <v>490480</v>
       </c>
       <c r="R55" t="n">
-        <v>6763833</v>
+        <v>6763872</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6542,7 +6537,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6552,7 +6547,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6561,63 +6556,69 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130789494</v>
+        <v>130755323</v>
       </c>
       <c r="B56" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490480</v>
+        <v>490451</v>
       </c>
       <c r="R56" t="n">
-        <v>6763872</v>
+        <v>6763833</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6649,7 +6650,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6659,7 +6660,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6668,19 +6669,18 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -4278,50 +4278,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130757247</v>
+        <v>130754851</v>
       </c>
       <c r="B35" t="n">
-        <v>5197</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490467</v>
+        <v>490449</v>
       </c>
       <c r="R35" t="n">
-        <v>6763573</v>
+        <v>6763949</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4353,7 +4348,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4363,7 +4358,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,7 +4390,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130754851</v>
+        <v>130757412</v>
       </c>
       <c r="B36" t="n">
         <v>79221</v>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490449</v>
+        <v>490381</v>
       </c>
       <c r="R36" t="n">
-        <v>6763949</v>
+        <v>6763583</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4470,12 +4470,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,7 +4497,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130757412</v>
+        <v>130789468</v>
       </c>
       <c r="B37" t="n">
         <v>79221</v>
@@ -4537,10 +4532,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490381</v>
+        <v>490321</v>
       </c>
       <c r="R37" t="n">
-        <v>6763583</v>
+        <v>6763593</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4572,7 +4567,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4582,7 +4577,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,63 +4586,69 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130789468</v>
+        <v>130757247</v>
       </c>
       <c r="B38" t="n">
-        <v>79221</v>
+        <v>5197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490321</v>
+        <v>490467</v>
       </c>
       <c r="R38" t="n">
-        <v>6763593</v>
+        <v>6763573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4679,7 +4680,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4689,7 +4690,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4698,29 +4699,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130789489</v>
+        <v>130755062</v>
       </c>
       <c r="B39" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490467</v>
+        <v>490434</v>
       </c>
       <c r="R39" t="n">
-        <v>6763913</v>
+        <v>6764045</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4787,7 +4792,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4797,7 +4802,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4806,26 +4816,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130789487</v>
+        <v>130789489</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -4860,10 +4869,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490472</v>
+        <v>490467</v>
       </c>
       <c r="R40" t="n">
-        <v>6763924</v>
+        <v>6763913</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,7 +4904,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4905,7 +4914,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4933,7 +4942,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130789497</v>
+        <v>130789487</v>
       </c>
       <c r="B41" t="n">
         <v>79221</v>
@@ -4968,10 +4977,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490525</v>
+        <v>490472</v>
       </c>
       <c r="R41" t="n">
-        <v>6763706</v>
+        <v>6763924</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,7 +5012,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5013,7 +5022,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,7 +5050,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755409</v>
+        <v>130789497</v>
       </c>
       <c r="B42" t="n">
         <v>79221</v>
@@ -5072,14 +5081,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490447</v>
+        <v>490525</v>
       </c>
       <c r="R42" t="n">
-        <v>6763817</v>
+        <v>6763706</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5111,7 +5120,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5121,7 +5130,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5130,25 +5139,26 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130757564</v>
+        <v>130755409</v>
       </c>
       <c r="B43" t="n">
         <v>79221</v>
@@ -5179,14 +5189,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490230</v>
+        <v>490447</v>
       </c>
       <c r="R43" t="n">
-        <v>6763582</v>
+        <v>6763817</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,7 +5228,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5228,7 +5238,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5255,10 +5265,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130755062</v>
+        <v>130757564</v>
       </c>
       <c r="B44" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5266,39 +5276,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490434</v>
+        <v>490230</v>
       </c>
       <c r="R44" t="n">
-        <v>6764045</v>
+        <v>6763582</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5330,7 +5335,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5340,12 +5345,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5372,45 +5372,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130754014</v>
+        <v>130758028</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490548</v>
+        <v>490175</v>
       </c>
       <c r="R45" t="n">
-        <v>6763654</v>
+        <v>6763613</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5442,7 +5447,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5452,7 +5457,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5479,7 +5484,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130754953</v>
+        <v>130754014</v>
       </c>
       <c r="B46" t="n">
         <v>79221</v>
@@ -5510,14 +5515,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490440</v>
+        <v>490548</v>
       </c>
       <c r="R46" t="n">
-        <v>6764028</v>
+        <v>6763654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5560,11 +5565,6 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5591,50 +5591,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130758028</v>
+        <v>130754953</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490175</v>
+        <v>490440</v>
       </c>
       <c r="R47" t="n">
-        <v>6763613</v>
+        <v>6764028</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5666,7 +5661,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5676,7 +5671,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130758572</v>
+        <v>130789459</v>
       </c>
       <c r="B48" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5714,39 +5714,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490494</v>
+        <v>490499</v>
       </c>
       <c r="R48" t="n">
-        <v>6763540</v>
+        <v>6763662</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5778,7 +5773,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5788,7 +5783,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5797,25 +5797,26 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130789459</v>
+        <v>130758032</v>
       </c>
       <c r="B49" t="n">
         <v>79221</v>
@@ -5846,14 +5847,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490499</v>
+        <v>490175</v>
       </c>
       <c r="R49" t="n">
-        <v>6763662</v>
+        <v>6763613</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5885,7 +5886,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5895,12 +5896,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>vid gran 250 år plus</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5909,29 +5905,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130758032</v>
+        <v>130758572</v>
       </c>
       <c r="B50" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5939,34 +5934,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490175</v>
+        <v>490494</v>
       </c>
       <c r="R50" t="n">
-        <v>6763613</v>
+        <v>6763540</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130754305</v>
+        <v>130754014</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490501</v>
+        <v>490548</v>
       </c>
       <c r="R2" t="n">
-        <v>6763773</v>
+        <v>6763654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130789469</v>
+        <v>130754083</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -816,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490373</v>
+        <v>490529</v>
       </c>
       <c r="R3" t="n">
-        <v>6763590</v>
+        <v>6763665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +865,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 bild, tall med gran till vänster</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,26 +886,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130789471</v>
+        <v>130754257</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -930,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490498</v>
+        <v>490525</v>
       </c>
       <c r="R4" t="n">
-        <v>6763669</v>
+        <v>6763729</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +978,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,59 +992,53 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130754287</v>
+        <v>130754307</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
@@ -1115,14 +1117,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130758328</v>
+        <v>130754701</v>
       </c>
       <c r="B6" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1146,14 +1148,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490200</v>
+        <v>490485</v>
       </c>
       <c r="R6" t="n">
-        <v>6763553</v>
+        <v>6763919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,14 +1224,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130789490</v>
+        <v>130754796</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1257,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490470</v>
+        <v>490463</v>
       </c>
       <c r="R7" t="n">
-        <v>6763909</v>
+        <v>6763939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,33 +1313,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130755448</v>
+        <v>130754851</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1361,14 +1362,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490441</v>
+        <v>490449</v>
       </c>
       <c r="R8" t="n">
-        <v>6763800</v>
+        <v>6763949</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,6 +1412,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 bild. På tallstam</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,14 +1443,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130789477</v>
+        <v>130754896</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1468,14 +1474,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490435</v>
+        <v>490446</v>
       </c>
       <c r="R9" t="n">
-        <v>6764047</v>
+        <v>6764008</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,33 +1532,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130789496</v>
+        <v>130754953</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1576,14 +1581,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490526</v>
+        <v>490440</v>
       </c>
       <c r="R10" t="n">
-        <v>6763737</v>
+        <v>6764028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1630,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 bild. Rikligt på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,33 +1644,32 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130789482</v>
+        <v>130754985</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1684,14 +1693,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490451</v>
+        <v>490434</v>
       </c>
       <c r="R11" t="n">
-        <v>6764011</v>
+        <v>6764045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,33 +1751,32 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130758082</v>
+        <v>130755409</v>
       </c>
       <c r="B12" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1792,14 +1800,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490186</v>
+        <v>490447</v>
       </c>
       <c r="R12" t="n">
-        <v>6763602</v>
+        <v>6763817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,50 +1876,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130757655</v>
+        <v>130755448</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Prikattmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490214</v>
+        <v>490441</v>
       </c>
       <c r="R13" t="n">
-        <v>6763590</v>
+        <v>6763800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1953,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,14 +1983,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130754257</v>
+        <v>130755955</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2015,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490525</v>
+        <v>490486</v>
       </c>
       <c r="R14" t="n">
-        <v>6763729</v>
+        <v>6763627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,11 +2064,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på tallstam</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,14 +2090,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130754083</v>
+        <v>130757159</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2121,19 +2119,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490529</v>
+        <v>490482</v>
       </c>
       <c r="R15" t="n">
-        <v>6763665</v>
+        <v>6763574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2160,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2175,12 +2170,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bild, tall med gran till vänster</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2179,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2208,14 +2197,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130789470</v>
+        <v>130757199</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2243,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490376</v>
+        <v>490467</v>
       </c>
       <c r="R16" t="n">
-        <v>6763596</v>
+        <v>6763573</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2288,7 +2277,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,69 +2286,63 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130757152</v>
+        <v>130757391</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490482</v>
+        <v>490381</v>
       </c>
       <c r="R17" t="n">
-        <v>6763574</v>
+        <v>6763583</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,11 +2385,6 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,14 +2411,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130789473</v>
+        <v>130757425</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2468,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490444</v>
+        <v>490361</v>
       </c>
       <c r="R18" t="n">
-        <v>6763969</v>
+        <v>6763574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,33 +2500,32 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130757425</v>
+        <v>130757564</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2572,14 +2549,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490361</v>
+        <v>490230</v>
       </c>
       <c r="R19" t="n">
-        <v>6763574</v>
+        <v>6763582</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,14 +2625,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130754307</v>
+        <v>130757742</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2679,14 +2656,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490501</v>
+        <v>490186</v>
       </c>
       <c r="R20" t="n">
-        <v>6763773</v>
+        <v>6763602</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2728,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2755,14 +2732,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130757199</v>
+        <v>130758032</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2786,14 +2763,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490467</v>
+        <v>490175</v>
       </c>
       <c r="R21" t="n">
-        <v>6763573</v>
+        <v>6763613</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,14 +2839,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130789474</v>
+        <v>130758292</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2893,14 +2870,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490445</v>
+        <v>490171</v>
       </c>
       <c r="R22" t="n">
-        <v>6763972</v>
+        <v>6763553</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2909,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2942,7 +2919,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,33 +2928,32 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130755955</v>
+        <v>130758328</v>
       </c>
       <c r="B23" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3001,14 +2977,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490486</v>
+        <v>490200</v>
       </c>
       <c r="R23" t="n">
-        <v>6763627</v>
+        <v>6763553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3016,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3026,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,14 +3053,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130789495</v>
+        <v>130789459</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3112,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490496</v>
+        <v>490499</v>
       </c>
       <c r="R24" t="n">
-        <v>6763849</v>
+        <v>6763662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3123,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,7 +3133,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>vid gran 250 år plus</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3185,14 +3166,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130754985</v>
+        <v>130789467</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3216,14 +3197,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490434</v>
+        <v>490152</v>
       </c>
       <c r="R25" t="n">
-        <v>6764045</v>
+        <v>6763632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3255,7 +3236,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3265,7 +3246,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,32 +3255,33 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130754896</v>
+        <v>130789468</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3323,14 +3305,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490446</v>
+        <v>490321</v>
       </c>
       <c r="R26" t="n">
-        <v>6764008</v>
+        <v>6763593</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,7 +3344,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3372,7 +3354,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3381,32 +3363,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130757159</v>
+        <v>130789469</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3434,10 +3417,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490482</v>
+        <v>490373</v>
       </c>
       <c r="R27" t="n">
-        <v>6763574</v>
+        <v>6763590</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3452,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3479,7 +3462,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3488,32 +3471,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130789472</v>
+        <v>130789470</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3541,10 +3525,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490450</v>
+        <v>490376</v>
       </c>
       <c r="R28" t="n">
-        <v>6763926</v>
+        <v>6763596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,7 +3560,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3586,7 +3570,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3614,14 +3598,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130754796</v>
+        <v>130789471</v>
       </c>
       <c r="B29" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3649,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490463</v>
+        <v>490498</v>
       </c>
       <c r="R29" t="n">
-        <v>6763939</v>
+        <v>6763669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3668,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,7 +3678,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3703,68 +3687,64 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130755667</v>
+        <v>130789472</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490444</v>
+        <v>490450</v>
       </c>
       <c r="R30" t="n">
-        <v>6763770</v>
+        <v>6763926</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,7 +3776,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3806,12 +3786,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 bilder</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3820,68 +3795,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130757715</v>
+        <v>130789473</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490186</v>
+        <v>490444</v>
       </c>
       <c r="R31" t="n">
-        <v>6763602</v>
+        <v>6763969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3884,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3923,7 +3894,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,32 +3903,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130789476</v>
+        <v>130789474</v>
       </c>
       <c r="B32" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3985,10 +3957,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490438</v>
+        <v>490445</v>
       </c>
       <c r="R32" t="n">
-        <v>6764018</v>
+        <v>6763972</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4020,7 +3992,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4030,7 +4002,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,11 +4033,11 @@
         <v>130789475</v>
       </c>
       <c r="B33" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4166,50 +4138,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130757236</v>
+        <v>130789476</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490467</v>
+        <v>490438</v>
       </c>
       <c r="R34" t="n">
-        <v>6763573</v>
+        <v>6764018</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,7 +4208,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4251,7 +4218,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,32 +4227,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130754851</v>
+        <v>130789477</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4313,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490449</v>
+        <v>490435</v>
       </c>
       <c r="R35" t="n">
-        <v>6763949</v>
+        <v>6764047</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4348,7 +4316,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4358,12 +4326,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 bild. På tallstam</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4372,32 +4335,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130757412</v>
+        <v>130789478</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4425,10 +4389,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490381</v>
+        <v>490436</v>
       </c>
       <c r="R36" t="n">
-        <v>6763583</v>
+        <v>6764052</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4460,7 +4424,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4470,7 +4434,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4479,32 +4443,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130789468</v>
+        <v>130789479</v>
       </c>
       <c r="B37" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4532,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490321</v>
+        <v>490444</v>
       </c>
       <c r="R37" t="n">
-        <v>6763593</v>
+        <v>6764042</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4567,7 +4532,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4577,7 +4542,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4605,50 +4570,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130757247</v>
+        <v>130789481</v>
       </c>
       <c r="B38" t="n">
-        <v>5197</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490467</v>
+        <v>490447</v>
       </c>
       <c r="R38" t="n">
-        <v>6763573</v>
+        <v>6764032</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4690,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4699,32 +4659,33 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130789489</v>
+        <v>130789482</v>
       </c>
       <c r="B39" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4752,10 +4713,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490467</v>
+        <v>490451</v>
       </c>
       <c r="R39" t="n">
-        <v>6763913</v>
+        <v>6764011</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4787,7 +4748,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4797,7 +4758,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4825,14 +4786,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130789487</v>
+        <v>130789483</v>
       </c>
       <c r="B40" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4860,10 +4821,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490472</v>
+        <v>490455</v>
       </c>
       <c r="R40" t="n">
-        <v>6763924</v>
+        <v>6763998</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,7 +4856,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4905,7 +4866,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4933,14 +4894,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130789497</v>
+        <v>130789484</v>
       </c>
       <c r="B41" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4968,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490525</v>
+        <v>490467</v>
       </c>
       <c r="R41" t="n">
-        <v>6763706</v>
+        <v>6763962</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,7 +4964,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5013,7 +4974,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,14 +5002,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130755409</v>
+        <v>130789485</v>
       </c>
       <c r="B42" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5072,14 +5033,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490447</v>
+        <v>490468</v>
       </c>
       <c r="R42" t="n">
-        <v>6763817</v>
+        <v>6763955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5111,7 +5072,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5121,7 +5082,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5130,32 +5091,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130757564</v>
+        <v>130789486</v>
       </c>
       <c r="B43" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5179,14 +5141,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>490230</v>
+        <v>490475</v>
       </c>
       <c r="R43" t="n">
-        <v>6763582</v>
+        <v>6763930</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5218,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5228,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5237,68 +5199,64 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130755062</v>
+        <v>130789487</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490434</v>
+        <v>490472</v>
       </c>
       <c r="R44" t="n">
-        <v>6764045</v>
+        <v>6763924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5330,7 +5288,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5340,12 +5298,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5354,32 +5307,33 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130754014</v>
+        <v>130789489</v>
       </c>
       <c r="B45" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5407,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490548</v>
+        <v>490467</v>
       </c>
       <c r="R45" t="n">
-        <v>6763654</v>
+        <v>6763913</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5442,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5452,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5461,32 +5415,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130754953</v>
+        <v>130789490</v>
       </c>
       <c r="B46" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5510,14 +5465,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490440</v>
+        <v>490470</v>
       </c>
       <c r="R46" t="n">
-        <v>6764028</v>
+        <v>6763909</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5549,7 +5504,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5559,12 +5514,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 bild. Rikligt på gran</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5573,68 +5523,64 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130758028</v>
+        <v>130789491</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490175</v>
+        <v>490481</v>
       </c>
       <c r="R47" t="n">
-        <v>6763613</v>
+        <v>6763891</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5666,7 +5612,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5676,7 +5622,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5685,32 +5631,33 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130789459</v>
+        <v>130789492</v>
       </c>
       <c r="B48" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5738,10 +5685,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490499</v>
+        <v>490481</v>
       </c>
       <c r="R48" t="n">
-        <v>6763662</v>
+        <v>6763889</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5773,7 +5720,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5783,12 +5730,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>vid gran 250 år plus</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5816,14 +5758,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130758032</v>
+        <v>130789493</v>
       </c>
       <c r="B49" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5847,14 +5789,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490175</v>
+        <v>490482</v>
       </c>
       <c r="R49" t="n">
-        <v>6763613</v>
+        <v>6763883</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5886,7 +5828,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5896,7 +5838,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5905,68 +5847,64 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130758572</v>
+        <v>130789494</v>
       </c>
       <c r="B50" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490494</v>
+        <v>490480</v>
       </c>
       <c r="R50" t="n">
-        <v>6763540</v>
+        <v>6763872</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5998,7 +5936,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6008,7 +5946,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6017,32 +5955,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Bo karlstens</t>
+          <t>Bo karlstens, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130789492</v>
+        <v>130789495</v>
       </c>
       <c r="B51" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6070,10 +6009,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490481</v>
+        <v>490496</v>
       </c>
       <c r="R51" t="n">
-        <v>6763889</v>
+        <v>6763849</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6105,7 +6044,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6115,7 +6054,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6143,14 +6082,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130789491</v>
+        <v>130789496</v>
       </c>
       <c r="B52" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6178,10 +6117,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490481</v>
+        <v>490526</v>
       </c>
       <c r="R52" t="n">
-        <v>6763891</v>
+        <v>6763737</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6213,7 +6152,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6223,7 +6162,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6251,14 +6190,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130789493</v>
+        <v>130789497</v>
       </c>
       <c r="B53" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6286,10 +6225,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490482</v>
+        <v>490525</v>
       </c>
       <c r="R53" t="n">
-        <v>6763883</v>
+        <v>6763706</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6321,7 +6260,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6331,7 +6270,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6362,11 +6301,11 @@
         <v>130789498</v>
       </c>
       <c r="B54" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6467,14 +6406,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130789494</v>
+        <v>130817408</v>
       </c>
       <c r="B55" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6498,14 +6437,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kråkbackarna, Dlr</t>
+          <t>Brunnvasselänget, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490480</v>
+        <v>490315</v>
       </c>
       <c r="R55" t="n">
-        <v>6763872</v>
+        <v>6763623</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6532,22 +6471,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6556,29 +6495,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130755323</v>
+        <v>130754287</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6586,39 +6524,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Prikattmyren, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490451</v>
+        <v>490501</v>
       </c>
       <c r="R56" t="n">
-        <v>6763833</v>
+        <v>6763773</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6687,45 +6625,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130817408</v>
+        <v>130757152</v>
       </c>
       <c r="B57" t="n">
-        <v>79244</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490315</v>
+        <v>490482</v>
       </c>
       <c r="R57" t="n">
-        <v>6763623</v>
+        <v>6763574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6752,22 +6695,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6787,34 +6735,34 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130816918</v>
+        <v>130758572</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6830,14 +6778,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490472</v>
+        <v>490494</v>
       </c>
       <c r="R58" t="n">
-        <v>6763537</v>
+        <v>6763540</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6864,27 +6812,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>2 bilder på gran</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6904,17 +6847,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130817398</v>
+        <v>130754667</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6942,19 +6885,19 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brunnvasselänget, Dlr</t>
+          <t>Kråkbackarna, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490315</v>
+        <v>490485</v>
       </c>
       <c r="R59" t="n">
-        <v>6763623</v>
+        <v>6763919</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6981,27 +6924,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>3 bilder på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,10 +6959,1605 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130755062</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Prikattmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>490434</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6764045</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130755667</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Prikattmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>490444</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6763770</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130758284</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>490171</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6763553</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130816918</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>490472</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6763537</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 bilder på gran</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130817398</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>490315</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6763623</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 bilder på tall</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130789463</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>490145</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6763625</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130757236</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>490467</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6763573</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130789464</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>490583</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6763583</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130757247</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>490467</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6763573</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130754305</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kråkbackarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>490501</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6763773</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130755323</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Prikattmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>490451</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6763833</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130757655</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>490214</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6763590</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130757715</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>490186</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6763602</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130758028</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Brunnvasselänget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>490175</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6763613</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62154-2025 artfynd.xlsx
+++ b/artfynd/A 62154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754014</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754083</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754257</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754307</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754701</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754796</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754851</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754896</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754953</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754985</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755409</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1980,6 +2040,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755448</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755955</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2194,6 +2264,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757159</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2301,6 +2376,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757199</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757391</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757425</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2622,6 +2712,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757564</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757742</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2836,6 +2936,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130758032</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2943,6 +3048,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130758292</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3050,6 +3160,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130758328</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3163,6 +3278,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789459</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3271,6 +3391,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789467</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3379,6 +3504,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789468</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3487,6 +3617,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789469</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3595,6 +3730,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789470</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3703,6 +3843,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789471</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3811,6 +3956,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789472</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3919,6 +4069,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789473</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4027,6 +4182,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789474</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4135,6 +4295,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789475</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4243,6 +4408,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789476</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4351,6 +4521,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789477</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4459,6 +4634,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789478</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4567,6 +4747,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789479</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4675,6 +4860,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789481</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4783,6 +4973,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789482</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4891,6 +5086,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789483</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4999,6 +5199,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789484</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5107,6 +5312,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789485</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5215,6 +5425,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789486</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5323,6 +5538,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789487</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5431,6 +5651,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789489</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5539,6 +5764,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789490</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5647,6 +5877,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789491</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5755,6 +5990,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789492</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5863,6 +6103,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789493</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5971,6 +6216,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789494</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6079,6 +6329,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789495</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6187,6 +6442,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789496</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6295,6 +6555,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789497</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6403,6 +6668,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789498</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6510,6 +6780,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130817408</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6622,6 +6897,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754287</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6739,6 +7019,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757152</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6851,6 +7136,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130758572</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6963,6 +7253,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754667</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7080,6 +7375,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755062</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7197,6 +7497,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755667</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7309,6 +7614,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130758284</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7426,6 +7736,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130816918</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7543,6 +7858,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130817398</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7663,6 +7983,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789463</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7775,6 +8100,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757236</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7886,6 +8216,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789464</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7998,6 +8333,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757247</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8110,6 +8450,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130754305</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8222,6 +8567,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130755323</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8334,6 +8684,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757655</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8446,6 +8801,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130757715</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8558,8 +8918,87 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130758028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>